--- a/artfynd/A 8773-2025 artfynd.xlsx
+++ b/artfynd/A 8773-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123317816</v>
+        <v>123317810</v>
       </c>
       <c r="B2" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>33</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>394154</v>
+        <v>394012</v>
       </c>
       <c r="R2" t="n">
-        <v>6504379</v>
+        <v>6504408</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -797,7 +797,7 @@
         <v>123317812</v>
       </c>
       <c r="B3" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -913,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123317828</v>
+        <v>123317814</v>
       </c>
       <c r="B4" t="n">
-        <v>95136</v>
+        <v>98368</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,38 +925,50 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Otterstad 1:7, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>394154</v>
+        <v>394108</v>
       </c>
       <c r="R4" t="n">
-        <v>6504379</v>
+        <v>6504203</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -997,6 +1009,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1019,10 +1032,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123317814</v>
+        <v>123317822</v>
       </c>
       <c r="B5" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1054,7 +1067,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1071,10 +1084,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>394108</v>
+        <v>393947</v>
       </c>
       <c r="R5" t="n">
-        <v>6504203</v>
+        <v>6504225</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1138,10 +1151,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123317813</v>
+        <v>123317816</v>
       </c>
       <c r="B6" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1173,7 +1186,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1190,10 +1203,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>394088</v>
+        <v>394154</v>
       </c>
       <c r="R6" t="n">
-        <v>6504114</v>
+        <v>6504379</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1257,10 +1270,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123317818</v>
+        <v>123317819</v>
       </c>
       <c r="B7" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1292,7 +1305,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1309,10 +1322,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>394150</v>
+        <v>394087</v>
       </c>
       <c r="R7" t="n">
-        <v>6504272</v>
+        <v>6504109</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1376,10 +1389,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123317817</v>
+        <v>123317818</v>
       </c>
       <c r="B8" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1428,10 +1441,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>394139</v>
+        <v>394150</v>
       </c>
       <c r="R8" t="n">
-        <v>6504327</v>
+        <v>6504272</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1495,10 +1508,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123317808</v>
+        <v>123317817</v>
       </c>
       <c r="B9" t="n">
-        <v>57494</v>
+        <v>98368</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1507,35 +1520,39 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1543,10 +1560,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>393947</v>
+        <v>394139</v>
       </c>
       <c r="R9" t="n">
-        <v>6504308</v>
+        <v>6504327</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1587,6 +1604,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1609,10 +1627,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123317827</v>
+        <v>123317823</v>
       </c>
       <c r="B10" t="n">
-        <v>105471</v>
+        <v>98368</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1621,30 +1639,30 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1661,10 +1679,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>394111</v>
+        <v>394108</v>
       </c>
       <c r="R10" t="n">
-        <v>6504177</v>
+        <v>6504389</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1728,10 +1746,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123317820</v>
+        <v>123317813</v>
       </c>
       <c r="B11" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1763,7 +1781,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1780,10 +1798,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>394159</v>
+        <v>394088</v>
       </c>
       <c r="R11" t="n">
-        <v>6504371</v>
+        <v>6504114</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1850,7 +1868,7 @@
         <v>123317801</v>
       </c>
       <c r="B12" t="n">
-        <v>94776</v>
+        <v>94779</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1949,10 +1967,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123317825</v>
+        <v>123317820</v>
       </c>
       <c r="B13" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1984,7 +2002,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2001,10 +2019,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>394022</v>
+        <v>394159</v>
       </c>
       <c r="R13" t="n">
-        <v>6504439</v>
+        <v>6504371</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2068,10 +2086,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123317824</v>
+        <v>123317828</v>
       </c>
       <c r="B14" t="n">
-        <v>98365</v>
+        <v>95139</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2080,50 +2098,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Otterstad 1:7, Vg</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>394136</v>
+        <v>394154</v>
       </c>
       <c r="R14" t="n">
-        <v>6504304</v>
+        <v>6504379</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2164,7 +2170,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2187,10 +2192,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123317811</v>
+        <v>123317821</v>
       </c>
       <c r="B15" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2222,7 +2227,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2239,10 +2244,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>394139</v>
+        <v>394117</v>
       </c>
       <c r="R15" t="n">
-        <v>6504335</v>
+        <v>6504168</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2306,10 +2311,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123317810</v>
+        <v>123317827</v>
       </c>
       <c r="B16" t="n">
-        <v>98365</v>
+        <v>105474</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2318,30 +2323,30 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2358,10 +2363,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>394012</v>
+        <v>394111</v>
       </c>
       <c r="R16" t="n">
-        <v>6504408</v>
+        <v>6504177</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2425,10 +2430,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123317804</v>
+        <v>123317825</v>
       </c>
       <c r="B17" t="n">
-        <v>91640</v>
+        <v>98368</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2437,38 +2442,50 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Otterstad 1:7, Vg</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>394108</v>
+        <v>394022</v>
       </c>
       <c r="R17" t="n">
-        <v>6504203</v>
+        <v>6504439</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2509,6 +2526,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2531,10 +2549,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123317823</v>
+        <v>123317804</v>
       </c>
       <c r="B18" t="n">
-        <v>98365</v>
+        <v>91643</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2543,40 +2561,28 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Otterstad 1:7, Vg</t>
@@ -2586,7 +2592,7 @@
         <v>394108</v>
       </c>
       <c r="R18" t="n">
-        <v>6504389</v>
+        <v>6504203</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2627,7 +2633,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2650,10 +2655,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123317809</v>
+        <v>123317824</v>
       </c>
       <c r="B19" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2685,7 +2690,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2702,10 +2707,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>394112</v>
+        <v>394136</v>
       </c>
       <c r="R19" t="n">
-        <v>6504193</v>
+        <v>6504304</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2772,7 +2777,7 @@
         <v>123317815</v>
       </c>
       <c r="B20" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2888,10 +2893,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123317819</v>
+        <v>123317811</v>
       </c>
       <c r="B21" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2923,7 +2928,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>28</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2940,10 +2945,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>394087</v>
+        <v>394139</v>
       </c>
       <c r="R21" t="n">
-        <v>6504109</v>
+        <v>6504335</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -3007,10 +3012,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123317822</v>
+        <v>123317809</v>
       </c>
       <c r="B22" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3042,7 +3047,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>42</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3059,10 +3064,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>393947</v>
+        <v>394112</v>
       </c>
       <c r="R22" t="n">
-        <v>6504225</v>
+        <v>6504193</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3126,10 +3131,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123317821</v>
+        <v>123317808</v>
       </c>
       <c r="B23" t="n">
-        <v>98365</v>
+        <v>57497</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3138,39 +3143,35 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3178,10 +3179,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>394117</v>
+        <v>393947</v>
       </c>
       <c r="R23" t="n">
-        <v>6504168</v>
+        <v>6504308</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3222,7 +3223,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 8773-2025 artfynd.xlsx
+++ b/artfynd/A 8773-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123317810</v>
+        <v>123317828</v>
       </c>
       <c r="B2" t="n">
-        <v>98368</v>
+        <v>95141</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,50 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Otterstad 1:7, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>394012</v>
+        <v>394154</v>
       </c>
       <c r="R2" t="n">
-        <v>6504408</v>
+        <v>6504379</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -771,7 +759,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -794,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123317812</v>
+        <v>123317811</v>
       </c>
       <c r="B3" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -829,7 +816,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>28</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -846,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>394109</v>
+        <v>394139</v>
       </c>
       <c r="R3" t="n">
-        <v>6504115</v>
+        <v>6504335</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -913,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123317814</v>
+        <v>123317827</v>
       </c>
       <c r="B4" t="n">
-        <v>98368</v>
+        <v>105476</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,30 +912,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -965,10 +952,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>394108</v>
+        <v>394111</v>
       </c>
       <c r="R4" t="n">
-        <v>6504203</v>
+        <v>6504177</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -1032,10 +1019,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123317822</v>
+        <v>123317814</v>
       </c>
       <c r="B5" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1067,7 +1054,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1084,10 +1071,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>393947</v>
+        <v>394108</v>
       </c>
       <c r="R5" t="n">
-        <v>6504225</v>
+        <v>6504203</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1151,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123317816</v>
+        <v>123317823</v>
       </c>
       <c r="B6" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1186,7 +1173,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1203,10 +1190,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>394154</v>
+        <v>394108</v>
       </c>
       <c r="R6" t="n">
-        <v>6504379</v>
+        <v>6504389</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1270,10 +1257,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123317819</v>
+        <v>123317816</v>
       </c>
       <c r="B7" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1305,7 +1292,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1322,10 +1309,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>394087</v>
+        <v>394154</v>
       </c>
       <c r="R7" t="n">
-        <v>6504109</v>
+        <v>6504379</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1389,10 +1376,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123317818</v>
+        <v>123317822</v>
       </c>
       <c r="B8" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1424,7 +1411,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1441,10 +1428,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>394150</v>
+        <v>393947</v>
       </c>
       <c r="R8" t="n">
-        <v>6504272</v>
+        <v>6504225</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1508,10 +1495,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123317817</v>
+        <v>123317818</v>
       </c>
       <c r="B9" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1560,10 +1547,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>394139</v>
+        <v>394150</v>
       </c>
       <c r="R9" t="n">
-        <v>6504327</v>
+        <v>6504272</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1627,10 +1614,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123317823</v>
+        <v>123317825</v>
       </c>
       <c r="B10" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1662,7 +1649,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1679,10 +1666,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>394108</v>
+        <v>394022</v>
       </c>
       <c r="R10" t="n">
-        <v>6504389</v>
+        <v>6504439</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1746,10 +1733,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123317813</v>
+        <v>123317820</v>
       </c>
       <c r="B11" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1781,7 +1768,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1798,10 +1785,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>394088</v>
+        <v>394159</v>
       </c>
       <c r="R11" t="n">
-        <v>6504114</v>
+        <v>6504371</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1865,10 +1852,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123317801</v>
+        <v>123317815</v>
       </c>
       <c r="B12" t="n">
-        <v>94779</v>
+        <v>98370</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1877,38 +1864,50 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2810</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Otterstad 1:7, Vg</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>393999</v>
+        <v>394144</v>
       </c>
       <c r="R12" t="n">
-        <v>6504375</v>
+        <v>6504350</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1949,6 +1948,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1960,17 +1960,21 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
+          <t>Jon Liljebäck, Ada  Arenander, Kurt-Anders Johansson, Liselotte Larsson , Ove Grönlund, Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Skogsgruppen Skaraborg</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123317820</v>
+        <v>123317821</v>
       </c>
       <c r="B13" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2019,10 +2023,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>394159</v>
+        <v>394117</v>
       </c>
       <c r="R13" t="n">
-        <v>6504371</v>
+        <v>6504168</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2086,10 +2090,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123317828</v>
+        <v>123317824</v>
       </c>
       <c r="B14" t="n">
-        <v>95139</v>
+        <v>98370</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2098,38 +2102,50 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Otterstad 1:7, Vg</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>394154</v>
+        <v>394136</v>
       </c>
       <c r="R14" t="n">
-        <v>6504379</v>
+        <v>6504304</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2170,6 +2186,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2192,10 +2209,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123317821</v>
+        <v>123317812</v>
       </c>
       <c r="B15" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2227,7 +2244,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2244,10 +2261,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>394117</v>
+        <v>394109</v>
       </c>
       <c r="R15" t="n">
-        <v>6504168</v>
+        <v>6504115</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2311,10 +2328,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123317827</v>
+        <v>123317817</v>
       </c>
       <c r="B16" t="n">
-        <v>105474</v>
+        <v>98370</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2323,30 +2340,30 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2363,10 +2380,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>394111</v>
+        <v>394139</v>
       </c>
       <c r="R16" t="n">
-        <v>6504177</v>
+        <v>6504327</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2430,10 +2447,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123317825</v>
+        <v>123317804</v>
       </c>
       <c r="B17" t="n">
-        <v>98368</v>
+        <v>91645</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2442,50 +2459,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Otterstad 1:7, Vg</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>394022</v>
+        <v>394108</v>
       </c>
       <c r="R17" t="n">
-        <v>6504439</v>
+        <v>6504203</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2526,7 +2531,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2549,10 +2553,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123317804</v>
+        <v>123317813</v>
       </c>
       <c r="B18" t="n">
-        <v>91643</v>
+        <v>98370</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2561,38 +2565,50 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Otterstad 1:7, Vg</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>394108</v>
+        <v>394088</v>
       </c>
       <c r="R18" t="n">
-        <v>6504203</v>
+        <v>6504114</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2633,6 +2649,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2655,10 +2672,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123317824</v>
+        <v>123317810</v>
       </c>
       <c r="B19" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2690,7 +2707,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>33</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2707,10 +2724,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>394136</v>
+        <v>394012</v>
       </c>
       <c r="R19" t="n">
-        <v>6504304</v>
+        <v>6504408</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2774,10 +2791,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123317815</v>
+        <v>123317809</v>
       </c>
       <c r="B20" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2809,7 +2826,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>42</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2826,10 +2843,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>394144</v>
+        <v>394112</v>
       </c>
       <c r="R20" t="n">
-        <v>6504350</v>
+        <v>6504193</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2893,10 +2910,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123317811</v>
+        <v>123317808</v>
       </c>
       <c r="B21" t="n">
-        <v>98368</v>
+        <v>57497</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2905,39 +2922,35 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2945,10 +2958,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>394139</v>
+        <v>393947</v>
       </c>
       <c r="R21" t="n">
-        <v>6504335</v>
+        <v>6504308</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2989,7 +3002,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3012,10 +3024,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123317809</v>
+        <v>123317819</v>
       </c>
       <c r="B22" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3047,7 +3059,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3064,10 +3076,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>394112</v>
+        <v>394087</v>
       </c>
       <c r="R22" t="n">
-        <v>6504193</v>
+        <v>6504109</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3131,10 +3143,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123317808</v>
+        <v>123317801</v>
       </c>
       <c r="B23" t="n">
-        <v>57497</v>
+        <v>94781</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3143,46 +3155,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Otterstad 1:7, Vg</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>393947</v>
+        <v>393999</v>
       </c>
       <c r="R23" t="n">
-        <v>6504308</v>
+        <v>6504375</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3234,14 +3238,10 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Jon Liljebäck, Ada  Arenander, Kurt-Anders Johansson, Liselotte Larsson , Ove Grönlund, Rolf-Göran Carlsson</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr">
-        <is>
-          <t>Skogsgruppen Skaraborg</t>
-        </is>
-      </c>
+          <t>Jon Liljebäck</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 8773-2025 artfynd.xlsx
+++ b/artfynd/A 8773-2025 artfynd.xlsx
@@ -2553,7 +2553,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123317813</v>
+        <v>123317810</v>
       </c>
       <c r="B18" t="n">
         <v>98370</v>
@@ -2588,7 +2588,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>33</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2605,10 +2605,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>394088</v>
+        <v>394012</v>
       </c>
       <c r="R18" t="n">
-        <v>6504114</v>
+        <v>6504408</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2672,7 +2672,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123317810</v>
+        <v>123317813</v>
       </c>
       <c r="B19" t="n">
         <v>98370</v>
@@ -2707,7 +2707,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2724,10 +2724,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>394012</v>
+        <v>394088</v>
       </c>
       <c r="R19" t="n">
-        <v>6504408</v>
+        <v>6504114</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2791,10 +2791,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123317809</v>
+        <v>123317808</v>
       </c>
       <c r="B20" t="n">
-        <v>98370</v>
+        <v>57497</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2803,39 +2803,35 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2843,10 +2839,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>394112</v>
+        <v>393947</v>
       </c>
       <c r="R20" t="n">
-        <v>6504193</v>
+        <v>6504308</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2887,7 +2883,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2910,10 +2905,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123317808</v>
+        <v>123317809</v>
       </c>
       <c r="B21" t="n">
-        <v>57497</v>
+        <v>98370</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2922,35 +2917,39 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2958,10 +2957,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>393947</v>
+        <v>394112</v>
       </c>
       <c r="R21" t="n">
-        <v>6504308</v>
+        <v>6504193</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -3002,6 +3001,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 8773-2025 artfynd.xlsx
+++ b/artfynd/A 8773-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123317828</v>
+        <v>123317810</v>
       </c>
       <c r="B2" t="n">
-        <v>95141</v>
+        <v>98376</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,50 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Otterstad 1:7, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>394154</v>
+        <v>394012</v>
       </c>
       <c r="R2" t="n">
-        <v>6504379</v>
+        <v>6504408</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -759,6 +771,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -781,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123317811</v>
+        <v>123317823</v>
       </c>
       <c r="B3" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -816,7 +829,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -833,10 +846,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>394139</v>
+        <v>394108</v>
       </c>
       <c r="R3" t="n">
-        <v>6504335</v>
+        <v>6504389</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -900,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123317827</v>
+        <v>123317814</v>
       </c>
       <c r="B4" t="n">
-        <v>105476</v>
+        <v>98376</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -912,30 +925,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -952,10 +965,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>394111</v>
+        <v>394108</v>
       </c>
       <c r="R4" t="n">
-        <v>6504177</v>
+        <v>6504203</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -1019,10 +1032,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123317814</v>
+        <v>123317809</v>
       </c>
       <c r="B5" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1054,7 +1067,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>42</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1071,10 +1084,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>394108</v>
+        <v>394112</v>
       </c>
       <c r="R5" t="n">
-        <v>6504203</v>
+        <v>6504193</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1138,10 +1151,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123317823</v>
+        <v>123317820</v>
       </c>
       <c r="B6" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1173,7 +1186,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1190,10 +1203,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>394108</v>
+        <v>394159</v>
       </c>
       <c r="R6" t="n">
-        <v>6504389</v>
+        <v>6504371</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1257,10 +1270,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123317816</v>
+        <v>123317811</v>
       </c>
       <c r="B7" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1292,7 +1305,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>28</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1309,10 +1322,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>394154</v>
+        <v>394139</v>
       </c>
       <c r="R7" t="n">
-        <v>6504379</v>
+        <v>6504335</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1376,10 +1389,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123317822</v>
+        <v>123317821</v>
       </c>
       <c r="B8" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1411,7 +1424,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1428,10 +1441,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>393947</v>
+        <v>394117</v>
       </c>
       <c r="R8" t="n">
-        <v>6504225</v>
+        <v>6504168</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1495,10 +1508,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123317818</v>
+        <v>123317824</v>
       </c>
       <c r="B9" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1530,7 +1543,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1547,10 +1560,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>394150</v>
+        <v>394136</v>
       </c>
       <c r="R9" t="n">
-        <v>6504272</v>
+        <v>6504304</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1614,10 +1627,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123317825</v>
+        <v>123317816</v>
       </c>
       <c r="B10" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1649,7 +1662,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1666,10 +1679,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>394022</v>
+        <v>394154</v>
       </c>
       <c r="R10" t="n">
-        <v>6504439</v>
+        <v>6504379</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1733,10 +1746,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123317820</v>
+        <v>123317804</v>
       </c>
       <c r="B11" t="n">
-        <v>98370</v>
+        <v>91651</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1745,50 +1758,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Otterstad 1:7, Vg</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>394159</v>
+        <v>394108</v>
       </c>
       <c r="R11" t="n">
-        <v>6504371</v>
+        <v>6504203</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1829,7 +1830,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1852,10 +1852,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123317815</v>
+        <v>123317808</v>
       </c>
       <c r="B12" t="n">
-        <v>98370</v>
+        <v>57497</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1864,39 +1864,35 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1904,10 +1900,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>394144</v>
+        <v>393947</v>
       </c>
       <c r="R12" t="n">
-        <v>6504350</v>
+        <v>6504308</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1948,7 +1944,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1971,10 +1966,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123317821</v>
+        <v>123317815</v>
       </c>
       <c r="B13" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2006,7 +2001,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2023,10 +2018,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>394117</v>
+        <v>394144</v>
       </c>
       <c r="R13" t="n">
-        <v>6504168</v>
+        <v>6504350</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2090,10 +2085,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123317824</v>
+        <v>123317819</v>
       </c>
       <c r="B14" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2125,7 +2120,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2142,10 +2137,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>394136</v>
+        <v>394087</v>
       </c>
       <c r="R14" t="n">
-        <v>6504304</v>
+        <v>6504109</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2209,10 +2204,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123317812</v>
+        <v>123317817</v>
       </c>
       <c r="B15" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2244,7 +2239,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2261,10 +2256,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>394109</v>
+        <v>394139</v>
       </c>
       <c r="R15" t="n">
-        <v>6504115</v>
+        <v>6504327</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2328,10 +2323,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123317817</v>
+        <v>123317812</v>
       </c>
       <c r="B16" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2363,7 +2358,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2380,10 +2375,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>394139</v>
+        <v>394109</v>
       </c>
       <c r="R16" t="n">
-        <v>6504327</v>
+        <v>6504115</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2447,10 +2442,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123317804</v>
+        <v>123317801</v>
       </c>
       <c r="B17" t="n">
-        <v>91645</v>
+        <v>94787</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2463,21 +2458,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3298</v>
+        <v>2810</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2487,10 +2482,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>394108</v>
+        <v>393999</v>
       </c>
       <c r="R17" t="n">
-        <v>6504203</v>
+        <v>6504375</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2542,21 +2537,17 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Jon Liljebäck, Ada  Arenander, Kurt-Anders Johansson, Liselotte Larsson , Ove Grönlund, Rolf-Göran Carlsson</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr">
-        <is>
-          <t>Skogsgruppen Skaraborg</t>
-        </is>
-      </c>
+          <t>Jon Liljebäck</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123317810</v>
+        <v>123317818</v>
       </c>
       <c r="B18" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2588,7 +2579,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2605,10 +2596,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>394012</v>
+        <v>394150</v>
       </c>
       <c r="R18" t="n">
-        <v>6504408</v>
+        <v>6504272</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2672,10 +2663,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123317813</v>
+        <v>123317827</v>
       </c>
       <c r="B19" t="n">
-        <v>98370</v>
+        <v>105482</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2684,30 +2675,30 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2724,10 +2715,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>394088</v>
+        <v>394111</v>
       </c>
       <c r="R19" t="n">
-        <v>6504114</v>
+        <v>6504177</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2791,10 +2782,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123317808</v>
+        <v>123317822</v>
       </c>
       <c r="B20" t="n">
-        <v>57497</v>
+        <v>98376</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2803,35 +2794,39 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2842,7 +2837,7 @@
         <v>393947</v>
       </c>
       <c r="R20" t="n">
-        <v>6504308</v>
+        <v>6504225</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2883,6 +2878,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2905,10 +2901,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123317809</v>
+        <v>123317825</v>
       </c>
       <c r="B21" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2940,7 +2936,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2957,10 +2953,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>394112</v>
+        <v>394022</v>
       </c>
       <c r="R21" t="n">
-        <v>6504193</v>
+        <v>6504439</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -3024,10 +3020,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123317819</v>
+        <v>123317828</v>
       </c>
       <c r="B22" t="n">
-        <v>98370</v>
+        <v>95147</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3036,50 +3032,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Otterstad 1:7, Vg</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>394087</v>
+        <v>394154</v>
       </c>
       <c r="R22" t="n">
-        <v>6504109</v>
+        <v>6504379</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3120,7 +3104,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3143,10 +3126,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123317801</v>
+        <v>123317813</v>
       </c>
       <c r="B23" t="n">
-        <v>94781</v>
+        <v>98376</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3155,38 +3138,50 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2810</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Otterstad 1:7, Vg</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>393999</v>
+        <v>394088</v>
       </c>
       <c r="R23" t="n">
-        <v>6504375</v>
+        <v>6504114</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3227,6 +3222,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3238,10 +3234,14 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr"/>
+          <t>Jon Liljebäck, Ada  Arenander, Kurt-Anders Johansson, Liselotte Larsson , Ove Grönlund, Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Skogsgruppen Skaraborg</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 8773-2025 artfynd.xlsx
+++ b/artfynd/A 8773-2025 artfynd.xlsx
@@ -2676,10 +2676,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123317828</v>
+        <v>123317804</v>
       </c>
       <c r="B19" t="n">
-        <v>95150</v>
+        <v>91654</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2692,21 +2692,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2180</v>
+        <v>3298</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2716,10 +2716,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>394154</v>
+        <v>394108</v>
       </c>
       <c r="R19" t="n">
-        <v>6504379</v>
+        <v>6504203</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2782,10 +2782,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123317804</v>
+        <v>123317811</v>
       </c>
       <c r="B20" t="n">
-        <v>91654</v>
+        <v>98379</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2794,38 +2794,50 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Otterstad 1:7, Vg</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>394108</v>
+        <v>394139</v>
       </c>
       <c r="R20" t="n">
-        <v>6504203</v>
+        <v>6504335</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2866,6 +2878,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2888,10 +2901,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123317811</v>
+        <v>123317828</v>
       </c>
       <c r="B21" t="n">
-        <v>98379</v>
+        <v>95150</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2900,50 +2913,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Otterstad 1:7, Vg</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>394139</v>
+        <v>394154</v>
       </c>
       <c r="R21" t="n">
-        <v>6504335</v>
+        <v>6504379</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2984,7 +2985,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 8773-2025 artfynd.xlsx
+++ b/artfynd/A 8773-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123317822</v>
+        <v>123317810</v>
       </c>
       <c r="B2" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>33</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>393947</v>
+        <v>394012</v>
       </c>
       <c r="R2" t="n">
-        <v>6504225</v>
+        <v>6504408</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -794,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123317810</v>
+        <v>123317815</v>
       </c>
       <c r="B3" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -829,7 +829,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -846,10 +846,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>394012</v>
+        <v>394144</v>
       </c>
       <c r="R3" t="n">
-        <v>6504408</v>
+        <v>6504350</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -913,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123317821</v>
+        <v>123317804</v>
       </c>
       <c r="B4" t="n">
-        <v>98379</v>
+        <v>91671</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,50 +925,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Otterstad 1:7, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>394117</v>
+        <v>394108</v>
       </c>
       <c r="R4" t="n">
-        <v>6504168</v>
+        <v>6504203</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -1009,7 +997,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1032,10 +1019,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123317819</v>
+        <v>123317828</v>
       </c>
       <c r="B5" t="n">
-        <v>98379</v>
+        <v>95167</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1044,50 +1031,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Otterstad 1:7, Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>394087</v>
+        <v>394154</v>
       </c>
       <c r="R5" t="n">
-        <v>6504109</v>
+        <v>6504379</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1128,7 +1103,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1140,7 +1114,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jon Liljebäck, Ada  Arenander, Kurt-Anders Johansson, Liselotte Larsson , Ove Grönlund, Rolf-Göran Carlsson</t>
+          <t>Rolf-Göran Carlsson, Ove Grönlund, Liselotte Larsson , Kurt-Anders Johansson, Ada  Arenander, Jon Liljebäck</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1151,10 +1125,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123317817</v>
+        <v>123317822</v>
       </c>
       <c r="B6" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1186,7 +1160,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1203,10 +1177,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>394139</v>
+        <v>393947</v>
       </c>
       <c r="R6" t="n">
-        <v>6504327</v>
+        <v>6504225</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1273,7 +1247,7 @@
         <v>123317812</v>
       </c>
       <c r="B7" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1389,10 +1363,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123317823</v>
+        <v>123317813</v>
       </c>
       <c r="B8" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1424,7 +1398,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1441,10 +1415,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>394108</v>
+        <v>394088</v>
       </c>
       <c r="R8" t="n">
-        <v>6504389</v>
+        <v>6504114</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1508,10 +1482,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123317824</v>
+        <v>123317814</v>
       </c>
       <c r="B9" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1543,7 +1517,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1560,10 +1534,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>394136</v>
+        <v>394108</v>
       </c>
       <c r="R9" t="n">
-        <v>6504304</v>
+        <v>6504203</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1627,10 +1601,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123317816</v>
+        <v>123317817</v>
       </c>
       <c r="B10" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1662,7 +1636,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1679,10 +1653,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>394154</v>
+        <v>394139</v>
       </c>
       <c r="R10" t="n">
-        <v>6504379</v>
+        <v>6504327</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1749,7 +1723,7 @@
         <v>123317820</v>
       </c>
       <c r="B11" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1865,10 +1839,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123317825</v>
+        <v>123317824</v>
       </c>
       <c r="B12" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1900,7 +1874,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1917,10 +1891,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>394022</v>
+        <v>394136</v>
       </c>
       <c r="R12" t="n">
-        <v>6504439</v>
+        <v>6504304</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1984,10 +1958,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123317809</v>
+        <v>123317816</v>
       </c>
       <c r="B13" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2019,7 +1993,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2036,10 +2010,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>394112</v>
+        <v>394154</v>
       </c>
       <c r="R13" t="n">
-        <v>6504193</v>
+        <v>6504379</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2103,10 +2077,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123317814</v>
+        <v>123317809</v>
       </c>
       <c r="B14" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2138,7 +2112,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>42</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2155,10 +2129,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>394108</v>
+        <v>394112</v>
       </c>
       <c r="R14" t="n">
-        <v>6504203</v>
+        <v>6504193</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2222,10 +2196,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123317808</v>
+        <v>123317821</v>
       </c>
       <c r="B15" t="n">
-        <v>57497</v>
+        <v>98396</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2234,35 +2208,39 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2270,10 +2248,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>393947</v>
+        <v>394117</v>
       </c>
       <c r="R15" t="n">
-        <v>6504308</v>
+        <v>6504168</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2314,6 +2292,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2336,10 +2315,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123317815</v>
+        <v>123317819</v>
       </c>
       <c r="B16" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2371,7 +2350,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2388,10 +2367,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>394144</v>
+        <v>394087</v>
       </c>
       <c r="R16" t="n">
-        <v>6504350</v>
+        <v>6504109</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2455,10 +2434,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123317818</v>
+        <v>123317825</v>
       </c>
       <c r="B17" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2490,7 +2469,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2507,10 +2486,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>394150</v>
+        <v>394022</v>
       </c>
       <c r="R17" t="n">
-        <v>6504272</v>
+        <v>6504439</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2574,10 +2553,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123317801</v>
+        <v>123317808</v>
       </c>
       <c r="B18" t="n">
-        <v>94790</v>
+        <v>57503</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2586,38 +2565,46 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Otterstad 1:7, Vg</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>393999</v>
+        <v>393947</v>
       </c>
       <c r="R18" t="n">
-        <v>6504375</v>
+        <v>6504308</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2669,17 +2656,21 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr"/>
+          <t>Jon Liljebäck, Ada  Arenander, Kurt-Anders Johansson, Liselotte Larsson , Ove Grönlund, Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Skogsgruppen Skaraborg</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123317804</v>
+        <v>123317801</v>
       </c>
       <c r="B19" t="n">
-        <v>91654</v>
+        <v>94807</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2692,21 +2683,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3298</v>
+        <v>2810</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2716,10 +2707,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>394108</v>
+        <v>393999</v>
       </c>
       <c r="R19" t="n">
-        <v>6504203</v>
+        <v>6504375</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2771,21 +2762,17 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Jon Liljebäck, Ada  Arenander, Kurt-Anders Johansson, Liselotte Larsson , Ove Grönlund, Rolf-Göran Carlsson</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr">
-        <is>
-          <t>Skogsgruppen Skaraborg</t>
-        </is>
-      </c>
+          <t>Jon Liljebäck</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
         <v>123317811</v>
       </c>
       <c r="B20" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2901,10 +2888,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123317828</v>
+        <v>123317818</v>
       </c>
       <c r="B21" t="n">
-        <v>95150</v>
+        <v>98396</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2913,38 +2900,50 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Otterstad 1:7, Vg</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>394154</v>
+        <v>394150</v>
       </c>
       <c r="R21" t="n">
-        <v>6504379</v>
+        <v>6504272</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2985,6 +2984,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3010,7 +3010,7 @@
         <v>123317827</v>
       </c>
       <c r="B22" t="n">
-        <v>105485</v>
+        <v>105502</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3126,10 +3126,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123317813</v>
+        <v>123317823</v>
       </c>
       <c r="B23" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3161,7 +3161,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3178,10 +3178,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>394088</v>
+        <v>394108</v>
       </c>
       <c r="R23" t="n">
-        <v>6504114</v>
+        <v>6504389</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>

--- a/artfynd/A 8773-2025 artfynd.xlsx
+++ b/artfynd/A 8773-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3243,6 +3243,446 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>123856271</v>
+      </c>
+      <c r="B24" t="n">
+        <v>91258</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>73</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Veckticka</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Flavidoporia pulvinascens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Pilát) Audet</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Otterstad 1:7, Vg</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>393935</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6504313</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Lidköping</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Otterstad</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>Avverknngsanmäld barrskog med hällmarker</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson, Jon Liljebäck, Ove Grönlund, Ada  Arenander, Liselotte Larsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>123856267</v>
+      </c>
+      <c r="B25" t="n">
+        <v>91389</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>4217</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Blodticka</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Meruliopsis taxicola</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Otterstad 1:7, Vg</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>393959</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6504224</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Lidköping</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Otterstad</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Avverknngsanmäld barrskog med hällmarker</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson, Jon Liljebäck, Ove Grönlund, Ada  Arenander, Liselotte Larsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>123856275</v>
+      </c>
+      <c r="B26" t="n">
+        <v>94813</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>2810</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus loreus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Otterstad 1:7, Vg</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>393991</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6504398</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Lidköping</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Otterstad</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Avverknngsanmäld barrskog med hällmarker</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson, Jon Liljebäck, Ove Grönlund, Ada  Arenander, Liselotte Larsson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>123856283</v>
+      </c>
+      <c r="B27" t="n">
+        <v>95173</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Otterstad 1:7, Vg</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>394108</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6504382</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Lidköping</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Otterstad</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Avverknngsanmäld barrskog med hällmarker</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson, Jon Liljebäck, Ove Grönlund, Ada  Arenander, Liselotte Larsson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 8773-2025 artfynd.xlsx
+++ b/artfynd/A 8773-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123317810</v>
+        <v>123317825</v>
       </c>
       <c r="B2" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>394012</v>
+        <v>394022</v>
       </c>
       <c r="R2" t="n">
-        <v>6504408</v>
+        <v>6504439</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -794,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123317815</v>
+        <v>123317810</v>
       </c>
       <c r="B3" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -829,7 +829,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>33</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -846,10 +846,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>394144</v>
+        <v>394012</v>
       </c>
       <c r="R3" t="n">
-        <v>6504350</v>
+        <v>6504408</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -913,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123317804</v>
+        <v>123317812</v>
       </c>
       <c r="B4" t="n">
-        <v>91671</v>
+        <v>98502</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,38 +925,50 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Otterstad 1:7, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>394108</v>
+        <v>394109</v>
       </c>
       <c r="R4" t="n">
-        <v>6504203</v>
+        <v>6504115</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -997,6 +1009,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1019,10 +1032,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123317828</v>
+        <v>123317813</v>
       </c>
       <c r="B5" t="n">
-        <v>95167</v>
+        <v>98502</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1031,38 +1044,50 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Otterstad 1:7, Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>394154</v>
+        <v>394088</v>
       </c>
       <c r="R5" t="n">
-        <v>6504379</v>
+        <v>6504114</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1103,6 +1128,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1114,7 +1140,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson, Ove Grönlund, Liselotte Larsson , Kurt-Anders Johansson, Ada  Arenander, Jon Liljebäck</t>
+          <t>Jon Liljebäck, Ada  Arenander, Kurt-Anders Johansson, Liselotte Larsson , Ove Grönlund, Rolf-Göran Carlsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1125,10 +1151,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123317822</v>
+        <v>123317820</v>
       </c>
       <c r="B6" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1160,7 +1186,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1177,10 +1203,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>393947</v>
+        <v>394159</v>
       </c>
       <c r="R6" t="n">
-        <v>6504225</v>
+        <v>6504371</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1244,10 +1270,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123317812</v>
+        <v>123317821</v>
       </c>
       <c r="B7" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1279,7 +1305,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1296,10 +1322,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>394109</v>
+        <v>394117</v>
       </c>
       <c r="R7" t="n">
-        <v>6504115</v>
+        <v>6504168</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1363,10 +1389,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123317813</v>
+        <v>123317808</v>
       </c>
       <c r="B8" t="n">
-        <v>98396</v>
+        <v>57506</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1375,39 +1401,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1415,10 +1437,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>394088</v>
+        <v>393947</v>
       </c>
       <c r="R8" t="n">
-        <v>6504114</v>
+        <v>6504308</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1459,7 +1481,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1485,7 +1506,7 @@
         <v>123317814</v>
       </c>
       <c r="B9" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1601,10 +1622,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123317817</v>
+        <v>123317822</v>
       </c>
       <c r="B10" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1636,7 +1657,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1653,10 +1674,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>394139</v>
+        <v>393947</v>
       </c>
       <c r="R10" t="n">
-        <v>6504327</v>
+        <v>6504225</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1720,10 +1741,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123317820</v>
+        <v>123317815</v>
       </c>
       <c r="B11" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1755,7 +1776,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1772,10 +1793,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>394159</v>
+        <v>394144</v>
       </c>
       <c r="R11" t="n">
-        <v>6504371</v>
+        <v>6504350</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1839,10 +1860,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123317824</v>
+        <v>123317827</v>
       </c>
       <c r="B12" t="n">
-        <v>98396</v>
+        <v>105518</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1851,30 +1872,30 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1891,10 +1912,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>394136</v>
+        <v>394111</v>
       </c>
       <c r="R12" t="n">
-        <v>6504304</v>
+        <v>6504177</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1958,10 +1979,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123317816</v>
+        <v>123317824</v>
       </c>
       <c r="B13" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1993,7 +2014,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2010,10 +2031,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>394154</v>
+        <v>394136</v>
       </c>
       <c r="R13" t="n">
-        <v>6504379</v>
+        <v>6504304</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2077,10 +2098,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123317809</v>
+        <v>123317828</v>
       </c>
       <c r="B14" t="n">
-        <v>98396</v>
+        <v>95173</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2089,50 +2110,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Otterstad 1:7, Vg</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>394112</v>
+        <v>394154</v>
       </c>
       <c r="R14" t="n">
-        <v>6504193</v>
+        <v>6504379</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2173,7 +2182,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2196,10 +2204,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123317821</v>
+        <v>123317809</v>
       </c>
       <c r="B15" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2231,7 +2239,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>42</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2248,10 +2256,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>394117</v>
+        <v>394112</v>
       </c>
       <c r="R15" t="n">
-        <v>6504168</v>
+        <v>6504193</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2318,7 +2326,7 @@
         <v>123317819</v>
       </c>
       <c r="B16" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2434,10 +2442,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123317825</v>
+        <v>123317811</v>
       </c>
       <c r="B17" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2469,7 +2477,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>28</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2486,10 +2494,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>394022</v>
+        <v>394139</v>
       </c>
       <c r="R17" t="n">
-        <v>6504439</v>
+        <v>6504335</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2553,10 +2561,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123317808</v>
+        <v>123317817</v>
       </c>
       <c r="B18" t="n">
-        <v>57503</v>
+        <v>98502</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2565,35 +2573,39 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2601,10 +2613,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>393947</v>
+        <v>394139</v>
       </c>
       <c r="R18" t="n">
-        <v>6504308</v>
+        <v>6504327</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2645,6 +2657,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2667,10 +2680,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123317801</v>
+        <v>123317804</v>
       </c>
       <c r="B19" t="n">
-        <v>94807</v>
+        <v>91676</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2683,21 +2696,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2810</v>
+        <v>3298</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2707,10 +2720,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>393999</v>
+        <v>394108</v>
       </c>
       <c r="R19" t="n">
-        <v>6504375</v>
+        <v>6504203</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2762,17 +2775,21 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr"/>
+          <t>Jon Liljebäck, Ada  Arenander, Kurt-Anders Johansson, Liselotte Larsson , Ove Grönlund, Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Skogsgruppen Skaraborg</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123317811</v>
+        <v>123317823</v>
       </c>
       <c r="B20" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2804,7 +2821,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2821,10 +2838,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>394139</v>
+        <v>394108</v>
       </c>
       <c r="R20" t="n">
-        <v>6504335</v>
+        <v>6504389</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2888,10 +2905,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123317818</v>
+        <v>123317816</v>
       </c>
       <c r="B21" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2923,7 +2940,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2940,10 +2957,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>394150</v>
+        <v>394154</v>
       </c>
       <c r="R21" t="n">
-        <v>6504272</v>
+        <v>6504379</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -3007,10 +3024,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123317827</v>
+        <v>123317801</v>
       </c>
       <c r="B22" t="n">
-        <v>105502</v>
+        <v>94813</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3023,46 +3040,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221144</v>
+        <v>2810</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Otterstad 1:7, Vg</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>394111</v>
+        <v>393999</v>
       </c>
       <c r="R22" t="n">
-        <v>6504177</v>
+        <v>6504375</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3103,7 +3108,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3115,21 +3119,17 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Jon Liljebäck, Ada  Arenander, Kurt-Anders Johansson, Liselotte Larsson , Ove Grönlund, Rolf-Göran Carlsson</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr">
-        <is>
-          <t>Skogsgruppen Skaraborg</t>
-        </is>
-      </c>
+          <t>Jon Liljebäck</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123317823</v>
+        <v>123317818</v>
       </c>
       <c r="B23" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3161,7 +3161,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3178,10 +3178,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>394108</v>
+        <v>394150</v>
       </c>
       <c r="R23" t="n">
-        <v>6504389</v>
+        <v>6504272</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3245,10 +3245,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123856271</v>
+        <v>123856283</v>
       </c>
       <c r="B24" t="n">
-        <v>91258</v>
+        <v>95173</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3257,49 +3257,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>73</v>
+        <v>2180</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Veckticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Flavidoporia pulvinascens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Pilát) Audet</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Otterstad 1:7, Vg</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>393935</v>
+        <v>394108</v>
       </c>
       <c r="R24" t="n">
-        <v>6504313</v>
+        <v>6504382</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3340,7 +3329,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3364,10 +3352,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123856267</v>
+        <v>123856271</v>
       </c>
       <c r="B25" t="n">
-        <v>91389</v>
+        <v>91258</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3376,38 +3364,49 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4217</v>
+        <v>73</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Flavidoporia pulvinascens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Pilát) Audet</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Otterstad 1:7, Vg</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>393959</v>
+        <v>393935</v>
       </c>
       <c r="R25" t="n">
-        <v>6504224</v>
+        <v>6504313</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3448,6 +3447,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3471,10 +3471,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123856275</v>
+        <v>123856267</v>
       </c>
       <c r="B26" t="n">
-        <v>94813</v>
+        <v>91389</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3487,21 +3487,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2810</v>
+        <v>4217</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3511,10 +3511,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>393991</v>
+        <v>393959</v>
       </c>
       <c r="R26" t="n">
-        <v>6504398</v>
+        <v>6504224</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3578,10 +3578,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123856283</v>
+        <v>123856275</v>
       </c>
       <c r="B27" t="n">
-        <v>95173</v>
+        <v>94813</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3594,21 +3594,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2180</v>
+        <v>2810</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3618,10 +3618,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>394108</v>
+        <v>393991</v>
       </c>
       <c r="R27" t="n">
-        <v>6504382</v>
+        <v>6504398</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>

--- a/artfynd/A 8773-2025 artfynd.xlsx
+++ b/artfynd/A 8773-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123317825</v>
+        <v>123317827</v>
       </c>
       <c r="B2" t="n">
-        <v>98502</v>
+        <v>105520</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>394022</v>
+        <v>394111</v>
       </c>
       <c r="R2" t="n">
-        <v>6504439</v>
+        <v>6504177</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -794,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123317810</v>
+        <v>123317819</v>
       </c>
       <c r="B3" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -829,7 +829,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -846,10 +846,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>394012</v>
+        <v>394087</v>
       </c>
       <c r="R3" t="n">
-        <v>6504408</v>
+        <v>6504109</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -913,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123317812</v>
+        <v>123317808</v>
       </c>
       <c r="B4" t="n">
-        <v>98502</v>
+        <v>57507</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,39 +925,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -965,10 +961,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>394109</v>
+        <v>393947</v>
       </c>
       <c r="R4" t="n">
-        <v>6504115</v>
+        <v>6504308</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -1009,7 +1005,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1032,10 +1027,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123317813</v>
+        <v>123317809</v>
       </c>
       <c r="B5" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1067,7 +1062,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>42</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1084,10 +1079,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>394088</v>
+        <v>394112</v>
       </c>
       <c r="R5" t="n">
-        <v>6504114</v>
+        <v>6504193</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1151,10 +1146,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123317820</v>
+        <v>123317814</v>
       </c>
       <c r="B6" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1186,7 +1181,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1203,10 +1198,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>394159</v>
+        <v>394108</v>
       </c>
       <c r="R6" t="n">
-        <v>6504371</v>
+        <v>6504203</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1270,10 +1265,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123317821</v>
+        <v>123317813</v>
       </c>
       <c r="B7" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1305,7 +1300,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1322,10 +1317,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>394117</v>
+        <v>394088</v>
       </c>
       <c r="R7" t="n">
-        <v>6504168</v>
+        <v>6504114</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1389,10 +1384,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123317808</v>
+        <v>123317815</v>
       </c>
       <c r="B8" t="n">
-        <v>57506</v>
+        <v>98504</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1401,35 +1396,39 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1437,10 +1436,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>393947</v>
+        <v>394144</v>
       </c>
       <c r="R8" t="n">
-        <v>6504308</v>
+        <v>6504350</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1481,6 +1480,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1503,10 +1503,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123317814</v>
+        <v>123317812</v>
       </c>
       <c r="B9" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>394108</v>
+        <v>394109</v>
       </c>
       <c r="R9" t="n">
-        <v>6504203</v>
+        <v>6504115</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1622,10 +1622,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123317822</v>
+        <v>123317823</v>
       </c>
       <c r="B10" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1674,10 +1674,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>393947</v>
+        <v>394108</v>
       </c>
       <c r="R10" t="n">
-        <v>6504225</v>
+        <v>6504389</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1741,10 +1741,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123317815</v>
+        <v>123317810</v>
       </c>
       <c r="B11" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>33</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1793,10 +1793,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>394144</v>
+        <v>394012</v>
       </c>
       <c r="R11" t="n">
-        <v>6504350</v>
+        <v>6504408</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1860,10 +1860,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123317827</v>
+        <v>123317821</v>
       </c>
       <c r="B12" t="n">
-        <v>105518</v>
+        <v>98504</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1872,30 +1872,30 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1912,10 +1912,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>394111</v>
+        <v>394117</v>
       </c>
       <c r="R12" t="n">
-        <v>6504177</v>
+        <v>6504168</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1979,10 +1979,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123317824</v>
+        <v>123317822</v>
       </c>
       <c r="B13" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2031,10 +2031,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>394136</v>
+        <v>393947</v>
       </c>
       <c r="R13" t="n">
-        <v>6504304</v>
+        <v>6504225</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2098,10 +2098,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123317828</v>
+        <v>123317804</v>
       </c>
       <c r="B14" t="n">
-        <v>95173</v>
+        <v>91678</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2114,21 +2114,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2180</v>
+        <v>3298</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2138,10 +2138,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>394154</v>
+        <v>394108</v>
       </c>
       <c r="R14" t="n">
-        <v>6504379</v>
+        <v>6504203</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2204,10 +2204,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123317809</v>
+        <v>123317820</v>
       </c>
       <c r="B15" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2256,10 +2256,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>394112</v>
+        <v>394159</v>
       </c>
       <c r="R15" t="n">
-        <v>6504193</v>
+        <v>6504371</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2323,10 +2323,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123317819</v>
+        <v>123317828</v>
       </c>
       <c r="B16" t="n">
-        <v>98502</v>
+        <v>95175</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2335,50 +2335,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Otterstad 1:7, Vg</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>394087</v>
+        <v>394154</v>
       </c>
       <c r="R16" t="n">
-        <v>6504109</v>
+        <v>6504379</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2419,7 +2407,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2442,10 +2429,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123317811</v>
+        <v>123317818</v>
       </c>
       <c r="B17" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2477,7 +2464,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2494,10 +2481,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>394139</v>
+        <v>394150</v>
       </c>
       <c r="R17" t="n">
-        <v>6504335</v>
+        <v>6504272</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2561,10 +2548,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123317817</v>
+        <v>123317816</v>
       </c>
       <c r="B18" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2596,7 +2583,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2613,10 +2600,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>394139</v>
+        <v>394154</v>
       </c>
       <c r="R18" t="n">
-        <v>6504327</v>
+        <v>6504379</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2680,10 +2667,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123317804</v>
+        <v>123317811</v>
       </c>
       <c r="B19" t="n">
-        <v>91676</v>
+        <v>98504</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2692,38 +2679,50 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Otterstad 1:7, Vg</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>394108</v>
+        <v>394139</v>
       </c>
       <c r="R19" t="n">
-        <v>6504203</v>
+        <v>6504335</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2764,6 +2763,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2786,10 +2786,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123317823</v>
+        <v>123317801</v>
       </c>
       <c r="B20" t="n">
-        <v>98502</v>
+        <v>94815</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2798,50 +2798,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>2810</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Otterstad 1:7, Vg</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>394108</v>
+        <v>393999</v>
       </c>
       <c r="R20" t="n">
-        <v>6504389</v>
+        <v>6504375</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2882,7 +2870,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2894,21 +2881,17 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Jon Liljebäck, Ada  Arenander, Kurt-Anders Johansson, Liselotte Larsson , Ove Grönlund, Rolf-Göran Carlsson</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr">
-        <is>
-          <t>Skogsgruppen Skaraborg</t>
-        </is>
-      </c>
+          <t>Jon Liljebäck</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123317816</v>
+        <v>123317824</v>
       </c>
       <c r="B21" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2940,7 +2923,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2957,10 +2940,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>394154</v>
+        <v>394136</v>
       </c>
       <c r="R21" t="n">
-        <v>6504379</v>
+        <v>6504304</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -3024,10 +3007,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123317801</v>
+        <v>123317825</v>
       </c>
       <c r="B22" t="n">
-        <v>94813</v>
+        <v>98504</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3036,38 +3019,50 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2810</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Otterstad 1:7, Vg</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>393999</v>
+        <v>394022</v>
       </c>
       <c r="R22" t="n">
-        <v>6504375</v>
+        <v>6504439</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3108,6 +3103,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3119,17 +3115,21 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr"/>
+          <t>Jon Liljebäck, Ada  Arenander, Kurt-Anders Johansson, Liselotte Larsson , Ove Grönlund, Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Skogsgruppen Skaraborg</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123317818</v>
+        <v>123317817</v>
       </c>
       <c r="B23" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3178,10 +3178,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>394150</v>
+        <v>394139</v>
       </c>
       <c r="R23" t="n">
-        <v>6504272</v>
+        <v>6504327</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3245,10 +3245,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123856283</v>
+        <v>123856275</v>
       </c>
       <c r="B24" t="n">
-        <v>95173</v>
+        <v>94815</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3261,21 +3261,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2180</v>
+        <v>2810</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3285,10 +3285,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>394108</v>
+        <v>393991</v>
       </c>
       <c r="R24" t="n">
-        <v>6504382</v>
+        <v>6504398</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3352,10 +3352,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123856271</v>
+        <v>123856267</v>
       </c>
       <c r="B25" t="n">
-        <v>91258</v>
+        <v>91391</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3364,49 +3364,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>73</v>
+        <v>4217</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Veckticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Flavidoporia pulvinascens</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Pilát) Audet</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Otterstad 1:7, Vg</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>393935</v>
+        <v>393959</v>
       </c>
       <c r="R25" t="n">
-        <v>6504313</v>
+        <v>6504224</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3447,7 +3436,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3464,17 +3452,17 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson, Jon Liljebäck, Ove Grönlund, Ada  Arenander, Liselotte Larsson</t>
+          <t>Liselotte Larsson , Ada  Arenander, Ove Grönlund, Jon Liljebäck, Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123856267</v>
+        <v>123856283</v>
       </c>
       <c r="B26" t="n">
-        <v>91389</v>
+        <v>95175</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3487,21 +3475,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4217</v>
+        <v>2180</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3511,10 +3499,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>393959</v>
+        <v>394108</v>
       </c>
       <c r="R26" t="n">
-        <v>6504224</v>
+        <v>6504382</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3578,10 +3566,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123856275</v>
+        <v>123856271</v>
       </c>
       <c r="B27" t="n">
-        <v>94813</v>
+        <v>91260</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3590,38 +3578,49 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2810</v>
+        <v>73</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Flavidoporia pulvinascens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Pilát) Audet</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Otterstad 1:7, Vg</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>393991</v>
+        <v>393935</v>
       </c>
       <c r="R27" t="n">
-        <v>6504398</v>
+        <v>6504313</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3662,6 +3661,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 8773-2025 artfynd.xlsx
+++ b/artfynd/A 8773-2025 artfynd.xlsx
@@ -913,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123317808</v>
+        <v>123317809</v>
       </c>
       <c r="B4" t="n">
-        <v>57507</v>
+        <v>98504</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,35 +925,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -961,10 +965,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>393947</v>
+        <v>394112</v>
       </c>
       <c r="R4" t="n">
-        <v>6504308</v>
+        <v>6504193</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -1005,6 +1009,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1027,7 +1032,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123317809</v>
+        <v>123317814</v>
       </c>
       <c r="B5" t="n">
         <v>98504</v>
@@ -1062,7 +1067,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1079,10 +1084,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>394112</v>
+        <v>394108</v>
       </c>
       <c r="R5" t="n">
-        <v>6504193</v>
+        <v>6504203</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1146,10 +1151,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123317814</v>
+        <v>123317808</v>
       </c>
       <c r="B6" t="n">
-        <v>98504</v>
+        <v>57507</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1158,39 +1163,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1198,10 +1199,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>394108</v>
+        <v>393947</v>
       </c>
       <c r="R6" t="n">
-        <v>6504203</v>
+        <v>6504308</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1242,7 +1243,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 8773-2025 artfynd.xlsx
+++ b/artfynd/A 8773-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123317827</v>
+        <v>123317804</v>
       </c>
       <c r="B2" t="n">
-        <v>105520</v>
+        <v>91678</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,46 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
+        <v>3298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Otterstad 1:7, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>394111</v>
+        <v>394108</v>
       </c>
       <c r="R2" t="n">
-        <v>6504177</v>
+        <v>6504203</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -771,7 +759,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -794,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123317819</v>
+        <v>123317827</v>
       </c>
       <c r="B3" t="n">
-        <v>98504</v>
+        <v>105095</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,30 +793,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -846,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>394087</v>
+        <v>394111</v>
       </c>
       <c r="R3" t="n">
-        <v>6504109</v>
+        <v>6504177</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -913,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123317809</v>
+        <v>123317816</v>
       </c>
       <c r="B4" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -948,7 +935,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -965,10 +952,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>394112</v>
+        <v>394154</v>
       </c>
       <c r="R4" t="n">
-        <v>6504193</v>
+        <v>6504379</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -1032,10 +1019,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123317814</v>
+        <v>123317801</v>
       </c>
       <c r="B5" t="n">
-        <v>98504</v>
+        <v>95323</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1044,50 +1031,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>2810</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Otterstad 1:7, Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>394108</v>
+        <v>393999</v>
       </c>
       <c r="R5" t="n">
-        <v>6504203</v>
+        <v>6504375</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1128,7 +1103,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1140,21 +1114,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jon Liljebäck, Ada  Arenander, Kurt-Anders Johansson, Liselotte Larsson , Ove Grönlund, Rolf-Göran Carlsson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Skogsgruppen Skaraborg</t>
-        </is>
-      </c>
+          <t>Jon Liljebäck</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123317808</v>
+        <v>123317817</v>
       </c>
       <c r="B6" t="n">
-        <v>57507</v>
+        <v>98079</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1163,35 +1133,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1199,10 +1173,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>393947</v>
+        <v>394139</v>
       </c>
       <c r="R6" t="n">
-        <v>6504308</v>
+        <v>6504327</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1243,6 +1217,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1265,10 +1240,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123317813</v>
+        <v>123317824</v>
       </c>
       <c r="B7" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1300,7 +1275,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1317,10 +1292,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>394088</v>
+        <v>394136</v>
       </c>
       <c r="R7" t="n">
-        <v>6504114</v>
+        <v>6504304</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1384,10 +1359,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123317815</v>
+        <v>123317820</v>
       </c>
       <c r="B8" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1419,7 +1394,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1436,10 +1411,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>394144</v>
+        <v>394159</v>
       </c>
       <c r="R8" t="n">
-        <v>6504350</v>
+        <v>6504371</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1503,10 +1478,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123317812</v>
+        <v>123317811</v>
       </c>
       <c r="B9" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1538,7 +1513,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>28</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1555,10 +1530,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>394109</v>
+        <v>394139</v>
       </c>
       <c r="R9" t="n">
-        <v>6504115</v>
+        <v>6504335</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1622,10 +1597,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123317823</v>
+        <v>123317818</v>
       </c>
       <c r="B10" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1657,7 +1632,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1674,10 +1649,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>394108</v>
+        <v>394150</v>
       </c>
       <c r="R10" t="n">
-        <v>6504389</v>
+        <v>6504272</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1741,10 +1716,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123317810</v>
+        <v>123317813</v>
       </c>
       <c r="B11" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1776,7 +1751,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1793,10 +1768,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>394012</v>
+        <v>394088</v>
       </c>
       <c r="R11" t="n">
-        <v>6504408</v>
+        <v>6504114</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1860,10 +1835,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123317821</v>
+        <v>123317808</v>
       </c>
       <c r="B12" t="n">
-        <v>98504</v>
+        <v>57507</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1872,39 +1847,35 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1912,10 +1883,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>394117</v>
+        <v>393947</v>
       </c>
       <c r="R12" t="n">
-        <v>6504168</v>
+        <v>6504308</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1956,7 +1927,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1979,10 +1949,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123317822</v>
+        <v>123317823</v>
       </c>
       <c r="B13" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2031,10 +2001,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>393947</v>
+        <v>394108</v>
       </c>
       <c r="R13" t="n">
-        <v>6504225</v>
+        <v>6504389</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2098,10 +2068,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123317804</v>
+        <v>123317809</v>
       </c>
       <c r="B14" t="n">
-        <v>91678</v>
+        <v>98079</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2110,38 +2080,50 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Otterstad 1:7, Vg</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>394108</v>
+        <v>394112</v>
       </c>
       <c r="R14" t="n">
-        <v>6504203</v>
+        <v>6504193</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2182,6 +2164,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2204,10 +2187,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123317820</v>
+        <v>123317828</v>
       </c>
       <c r="B15" t="n">
-        <v>98504</v>
+        <v>95683</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2216,50 +2199,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Otterstad 1:7, Vg</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>394159</v>
+        <v>394154</v>
       </c>
       <c r="R15" t="n">
-        <v>6504371</v>
+        <v>6504379</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2300,7 +2271,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2323,10 +2293,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123317828</v>
+        <v>123317822</v>
       </c>
       <c r="B16" t="n">
-        <v>95175</v>
+        <v>98079</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2335,38 +2305,50 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Otterstad 1:7, Vg</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>394154</v>
+        <v>393947</v>
       </c>
       <c r="R16" t="n">
-        <v>6504379</v>
+        <v>6504225</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2407,6 +2389,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2429,10 +2412,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123317818</v>
+        <v>123317814</v>
       </c>
       <c r="B17" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2464,7 +2447,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2481,10 +2464,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>394150</v>
+        <v>394108</v>
       </c>
       <c r="R17" t="n">
-        <v>6504272</v>
+        <v>6504203</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2548,10 +2531,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123317816</v>
+        <v>123317819</v>
       </c>
       <c r="B18" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2583,7 +2566,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2600,10 +2583,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>394154</v>
+        <v>394087</v>
       </c>
       <c r="R18" t="n">
-        <v>6504379</v>
+        <v>6504109</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2667,10 +2650,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123317811</v>
+        <v>123317810</v>
       </c>
       <c r="B19" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2702,7 +2685,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>33</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2719,10 +2702,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>394139</v>
+        <v>394012</v>
       </c>
       <c r="R19" t="n">
-        <v>6504335</v>
+        <v>6504408</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2786,10 +2769,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123317801</v>
+        <v>123317821</v>
       </c>
       <c r="B20" t="n">
-        <v>94815</v>
+        <v>98079</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2798,38 +2781,50 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2810</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Otterstad 1:7, Vg</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>393999</v>
+        <v>394117</v>
       </c>
       <c r="R20" t="n">
-        <v>6504375</v>
+        <v>6504168</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2870,6 +2865,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2881,17 +2877,21 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr"/>
+          <t>Jon Liljebäck, Ada  Arenander, Kurt-Anders Johansson, Liselotte Larsson , Ove Grönlund, Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Skogsgruppen Skaraborg</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123317824</v>
+        <v>123317812</v>
       </c>
       <c r="B21" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2940,10 +2940,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>394136</v>
+        <v>394109</v>
       </c>
       <c r="R21" t="n">
-        <v>6504304</v>
+        <v>6504115</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -3010,7 +3010,7 @@
         <v>123317825</v>
       </c>
       <c r="B22" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3126,10 +3126,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123317817</v>
+        <v>123317815</v>
       </c>
       <c r="B23" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3161,7 +3161,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3178,10 +3178,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>394139</v>
+        <v>394144</v>
       </c>
       <c r="R23" t="n">
-        <v>6504327</v>
+        <v>6504350</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3245,10 +3245,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123856275</v>
+        <v>123856271</v>
       </c>
       <c r="B24" t="n">
-        <v>94815</v>
+        <v>91260</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3257,38 +3257,49 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2810</v>
+        <v>73</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Flavidoporia pulvinascens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Pilát) Audet</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Otterstad 1:7, Vg</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>393991</v>
+        <v>393935</v>
       </c>
       <c r="R24" t="n">
-        <v>6504398</v>
+        <v>6504313</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3329,6 +3340,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3352,10 +3364,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123856267</v>
+        <v>123856275</v>
       </c>
       <c r="B25" t="n">
-        <v>91391</v>
+        <v>95323</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3368,21 +3380,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4217</v>
+        <v>2810</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3392,10 +3404,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>393959</v>
+        <v>393991</v>
       </c>
       <c r="R25" t="n">
-        <v>6504224</v>
+        <v>6504398</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3452,7 +3464,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Liselotte Larsson , Ada  Arenander, Ove Grönlund, Jon Liljebäck, Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson, Jon Liljebäck, Ove Grönlund, Ada  Arenander, Liselotte Larsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3462,7 +3474,7 @@
         <v>123856283</v>
       </c>
       <c r="B26" t="n">
-        <v>95175</v>
+        <v>95683</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3566,10 +3578,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123856271</v>
+        <v>123856267</v>
       </c>
       <c r="B27" t="n">
-        <v>91260</v>
+        <v>91391</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3578,49 +3590,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>73</v>
+        <v>4217</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Veckticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Flavidoporia pulvinascens</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Pilát) Audet</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Otterstad 1:7, Vg</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>393935</v>
+        <v>393959</v>
       </c>
       <c r="R27" t="n">
-        <v>6504313</v>
+        <v>6504224</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3661,7 +3662,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 8773-2025 artfynd.xlsx
+++ b/artfynd/A 8773-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123317804</v>
+        <v>123317815</v>
       </c>
       <c r="B2" t="n">
-        <v>91678</v>
+        <v>98079</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,50 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Otterstad 1:7, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>394108</v>
+        <v>394144</v>
       </c>
       <c r="R2" t="n">
-        <v>6504203</v>
+        <v>6504350</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -759,6 +771,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -781,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123317827</v>
+        <v>123317820</v>
       </c>
       <c r="B3" t="n">
-        <v>105095</v>
+        <v>98079</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,30 +806,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -833,10 +846,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>394111</v>
+        <v>394159</v>
       </c>
       <c r="R3" t="n">
-        <v>6504177</v>
+        <v>6504371</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -900,7 +913,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123317816</v>
+        <v>123317818</v>
       </c>
       <c r="B4" t="n">
         <v>98079</v>
@@ -935,7 +948,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -952,10 +965,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>394154</v>
+        <v>394150</v>
       </c>
       <c r="R4" t="n">
-        <v>6504379</v>
+        <v>6504272</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -1019,10 +1032,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123317801</v>
+        <v>123317827</v>
       </c>
       <c r="B5" t="n">
-        <v>95323</v>
+        <v>105095</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1035,34 +1048,46 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2810</v>
+        <v>221144</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Otterstad 1:7, Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>393999</v>
+        <v>394111</v>
       </c>
       <c r="R5" t="n">
-        <v>6504375</v>
+        <v>6504177</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1103,6 +1128,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1114,14 +1140,18 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Jon Liljebäck, Ada  Arenander, Kurt-Anders Johansson, Liselotte Larsson , Ove Grönlund, Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Skogsgruppen Skaraborg</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123317817</v>
+        <v>123317813</v>
       </c>
       <c r="B6" t="n">
         <v>98079</v>
@@ -1156,7 +1186,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1173,10 +1203,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>394139</v>
+        <v>394088</v>
       </c>
       <c r="R6" t="n">
-        <v>6504327</v>
+        <v>6504114</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1240,7 +1270,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123317824</v>
+        <v>123317814</v>
       </c>
       <c r="B7" t="n">
         <v>98079</v>
@@ -1275,7 +1305,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1292,10 +1322,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>394136</v>
+        <v>394108</v>
       </c>
       <c r="R7" t="n">
-        <v>6504304</v>
+        <v>6504203</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1359,7 +1389,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123317820</v>
+        <v>123317811</v>
       </c>
       <c r="B8" t="n">
         <v>98079</v>
@@ -1394,7 +1424,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>28</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1411,10 +1441,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>394159</v>
+        <v>394139</v>
       </c>
       <c r="R8" t="n">
-        <v>6504371</v>
+        <v>6504335</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1478,7 +1508,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123317811</v>
+        <v>123317817</v>
       </c>
       <c r="B9" t="n">
         <v>98079</v>
@@ -1513,7 +1543,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1533,7 +1563,7 @@
         <v>394139</v>
       </c>
       <c r="R9" t="n">
-        <v>6504335</v>
+        <v>6504327</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1597,10 +1627,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123317818</v>
+        <v>123317801</v>
       </c>
       <c r="B10" t="n">
-        <v>98079</v>
+        <v>95323</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1609,50 +1639,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>2810</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Otterstad 1:7, Vg</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>394150</v>
+        <v>393999</v>
       </c>
       <c r="R10" t="n">
-        <v>6504272</v>
+        <v>6504375</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1693,7 +1711,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1705,18 +1722,14 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Jon Liljebäck, Ada  Arenander, Kurt-Anders Johansson, Liselotte Larsson , Ove Grönlund, Rolf-Göran Carlsson</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>Skogsgruppen Skaraborg</t>
-        </is>
-      </c>
+          <t>Jon Liljebäck</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123317813</v>
+        <v>123317819</v>
       </c>
       <c r="B11" t="n">
         <v>98079</v>
@@ -1751,7 +1764,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1768,10 +1781,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>394088</v>
+        <v>394087</v>
       </c>
       <c r="R11" t="n">
-        <v>6504114</v>
+        <v>6504109</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1835,10 +1848,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123317808</v>
+        <v>123317828</v>
       </c>
       <c r="B12" t="n">
-        <v>57507</v>
+        <v>95683</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1847,46 +1860,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Otterstad 1:7, Vg</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>393947</v>
+        <v>394154</v>
       </c>
       <c r="R12" t="n">
-        <v>6504308</v>
+        <v>6504379</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1949,7 +1954,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123317823</v>
+        <v>123317821</v>
       </c>
       <c r="B13" t="n">
         <v>98079</v>
@@ -1984,7 +1989,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2001,10 +2006,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>394108</v>
+        <v>394117</v>
       </c>
       <c r="R13" t="n">
-        <v>6504389</v>
+        <v>6504168</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2068,7 +2073,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123317809</v>
+        <v>123317823</v>
       </c>
       <c r="B14" t="n">
         <v>98079</v>
@@ -2103,7 +2108,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2120,10 +2125,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>394112</v>
+        <v>394108</v>
       </c>
       <c r="R14" t="n">
-        <v>6504193</v>
+        <v>6504389</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2187,10 +2192,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123317828</v>
+        <v>123317822</v>
       </c>
       <c r="B15" t="n">
-        <v>95683</v>
+        <v>98079</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2199,38 +2204,50 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Otterstad 1:7, Vg</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>394154</v>
+        <v>393947</v>
       </c>
       <c r="R15" t="n">
-        <v>6504379</v>
+        <v>6504225</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2271,6 +2288,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2293,10 +2311,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123317822</v>
+        <v>123317804</v>
       </c>
       <c r="B16" t="n">
-        <v>98079</v>
+        <v>91678</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2305,50 +2323,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Otterstad 1:7, Vg</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>393947</v>
+        <v>394108</v>
       </c>
       <c r="R16" t="n">
-        <v>6504225</v>
+        <v>6504203</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2389,7 +2395,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2412,10 +2417,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123317814</v>
+        <v>123317808</v>
       </c>
       <c r="B17" t="n">
-        <v>98079</v>
+        <v>57507</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2424,39 +2429,35 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2464,10 +2465,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>394108</v>
+        <v>393947</v>
       </c>
       <c r="R17" t="n">
-        <v>6504203</v>
+        <v>6504308</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2508,7 +2509,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2531,7 +2531,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123317819</v>
+        <v>123317810</v>
       </c>
       <c r="B18" t="n">
         <v>98079</v>
@@ -2566,7 +2566,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>33</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2583,10 +2583,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>394087</v>
+        <v>394012</v>
       </c>
       <c r="R18" t="n">
-        <v>6504109</v>
+        <v>6504408</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2650,7 +2650,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123317810</v>
+        <v>123317809</v>
       </c>
       <c r="B19" t="n">
         <v>98079</v>
@@ -2685,7 +2685,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>42</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2702,10 +2702,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>394012</v>
+        <v>394112</v>
       </c>
       <c r="R19" t="n">
-        <v>6504408</v>
+        <v>6504193</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2769,7 +2769,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123317821</v>
+        <v>123317812</v>
       </c>
       <c r="B20" t="n">
         <v>98079</v>
@@ -2804,7 +2804,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2821,10 +2821,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>394117</v>
+        <v>394109</v>
       </c>
       <c r="R20" t="n">
-        <v>6504168</v>
+        <v>6504115</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2888,7 +2888,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123317812</v>
+        <v>123317824</v>
       </c>
       <c r="B21" t="n">
         <v>98079</v>
@@ -2923,7 +2923,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2940,10 +2940,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>394109</v>
+        <v>394136</v>
       </c>
       <c r="R21" t="n">
-        <v>6504115</v>
+        <v>6504304</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -3007,7 +3007,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123317825</v>
+        <v>123317816</v>
       </c>
       <c r="B22" t="n">
         <v>98079</v>
@@ -3042,7 +3042,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3059,10 +3059,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>394022</v>
+        <v>394154</v>
       </c>
       <c r="R22" t="n">
-        <v>6504439</v>
+        <v>6504379</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3126,7 +3126,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123317815</v>
+        <v>123317825</v>
       </c>
       <c r="B23" t="n">
         <v>98079</v>
@@ -3161,7 +3161,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3178,10 +3178,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>394144</v>
+        <v>394022</v>
       </c>
       <c r="R23" t="n">
-        <v>6504350</v>
+        <v>6504439</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3245,10 +3245,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123856271</v>
+        <v>123856267</v>
       </c>
       <c r="B24" t="n">
-        <v>91260</v>
+        <v>91391</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3257,49 +3257,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>73</v>
+        <v>4217</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Veckticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Flavidoporia pulvinascens</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Pilát) Audet</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Otterstad 1:7, Vg</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>393935</v>
+        <v>393959</v>
       </c>
       <c r="R24" t="n">
-        <v>6504313</v>
+        <v>6504224</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3340,7 +3329,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3578,10 +3566,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123856267</v>
+        <v>123856271</v>
       </c>
       <c r="B27" t="n">
-        <v>91391</v>
+        <v>91260</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3590,38 +3578,49 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4217</v>
+        <v>73</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Flavidoporia pulvinascens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Pilát) Audet</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Otterstad 1:7, Vg</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>393959</v>
+        <v>393935</v>
       </c>
       <c r="R27" t="n">
-        <v>6504224</v>
+        <v>6504313</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3662,6 +3661,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 8773-2025 artfynd.xlsx
+++ b/artfynd/A 8773-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123317815</v>
+        <v>123317804</v>
       </c>
       <c r="B2" t="n">
-        <v>98079</v>
+        <v>91678</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,50 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Otterstad 1:7, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>394144</v>
+        <v>394108</v>
       </c>
       <c r="R2" t="n">
-        <v>6504350</v>
+        <v>6504203</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -771,7 +759,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -794,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123317820</v>
+        <v>123317811</v>
       </c>
       <c r="B3" t="n">
         <v>98079</v>
@@ -829,7 +816,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>28</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -846,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>394159</v>
+        <v>394139</v>
       </c>
       <c r="R3" t="n">
-        <v>6504371</v>
+        <v>6504335</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -913,7 +900,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123317818</v>
+        <v>123317810</v>
       </c>
       <c r="B4" t="n">
         <v>98079</v>
@@ -948,7 +935,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>33</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -965,10 +952,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>394150</v>
+        <v>394012</v>
       </c>
       <c r="R4" t="n">
-        <v>6504272</v>
+        <v>6504408</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -1032,10 +1019,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123317827</v>
+        <v>123317809</v>
       </c>
       <c r="B5" t="n">
-        <v>105095</v>
+        <v>98079</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1044,30 +1031,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>42</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1084,10 +1071,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>394111</v>
+        <v>394112</v>
       </c>
       <c r="R5" t="n">
-        <v>6504177</v>
+        <v>6504193</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1151,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123317813</v>
+        <v>123317801</v>
       </c>
       <c r="B6" t="n">
-        <v>98079</v>
+        <v>95323</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1163,50 +1150,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>2810</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Otterstad 1:7, Vg</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>394088</v>
+        <v>393999</v>
       </c>
       <c r="R6" t="n">
-        <v>6504114</v>
+        <v>6504375</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1247,7 +1222,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1259,14 +1233,10 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jon Liljebäck, Ada  Arenander, Kurt-Anders Johansson, Liselotte Larsson , Ove Grönlund, Rolf-Göran Carlsson</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>Skogsgruppen Skaraborg</t>
-        </is>
-      </c>
+          <t>Jon Liljebäck</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1389,7 +1359,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123317811</v>
+        <v>123317823</v>
       </c>
       <c r="B8" t="n">
         <v>98079</v>
@@ -1424,7 +1394,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1441,10 +1411,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>394139</v>
+        <v>394108</v>
       </c>
       <c r="R8" t="n">
-        <v>6504335</v>
+        <v>6504389</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1508,7 +1478,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123317817</v>
+        <v>123317825</v>
       </c>
       <c r="B9" t="n">
         <v>98079</v>
@@ -1543,7 +1513,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1560,10 +1530,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>394139</v>
+        <v>394022</v>
       </c>
       <c r="R9" t="n">
-        <v>6504327</v>
+        <v>6504439</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1627,10 +1597,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123317801</v>
+        <v>123317820</v>
       </c>
       <c r="B10" t="n">
-        <v>95323</v>
+        <v>98079</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1639,38 +1609,50 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2810</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Otterstad 1:7, Vg</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>393999</v>
+        <v>394159</v>
       </c>
       <c r="R10" t="n">
-        <v>6504375</v>
+        <v>6504371</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1711,6 +1693,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1722,10 +1705,14 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
+          <t>Jon Liljebäck, Ada  Arenander, Kurt-Anders Johansson, Liselotte Larsson , Ove Grönlund, Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Skogsgruppen Skaraborg</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1848,10 +1835,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123317828</v>
+        <v>123317812</v>
       </c>
       <c r="B12" t="n">
-        <v>95683</v>
+        <v>98079</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1860,38 +1847,50 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Otterstad 1:7, Vg</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>394154</v>
+        <v>394109</v>
       </c>
       <c r="R12" t="n">
-        <v>6504379</v>
+        <v>6504115</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1932,6 +1931,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1954,7 +1954,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123317821</v>
+        <v>123317813</v>
       </c>
       <c r="B13" t="n">
         <v>98079</v>
@@ -1989,7 +1989,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2006,10 +2006,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>394117</v>
+        <v>394088</v>
       </c>
       <c r="R13" t="n">
-        <v>6504168</v>
+        <v>6504114</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2073,10 +2073,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123317823</v>
+        <v>123317827</v>
       </c>
       <c r="B14" t="n">
-        <v>98079</v>
+        <v>105095</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2085,30 +2085,30 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2125,10 +2125,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>394108</v>
+        <v>394111</v>
       </c>
       <c r="R14" t="n">
-        <v>6504389</v>
+        <v>6504177</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2192,7 +2192,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123317822</v>
+        <v>123317817</v>
       </c>
       <c r="B15" t="n">
         <v>98079</v>
@@ -2227,7 +2227,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2244,10 +2244,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>393947</v>
+        <v>394139</v>
       </c>
       <c r="R15" t="n">
-        <v>6504225</v>
+        <v>6504327</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2311,10 +2311,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123317804</v>
+        <v>123317824</v>
       </c>
       <c r="B16" t="n">
-        <v>91678</v>
+        <v>98079</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2323,38 +2323,50 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Otterstad 1:7, Vg</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>394108</v>
+        <v>394136</v>
       </c>
       <c r="R16" t="n">
-        <v>6504203</v>
+        <v>6504304</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2395,6 +2407,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2417,10 +2430,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123317808</v>
+        <v>123317828</v>
       </c>
       <c r="B17" t="n">
-        <v>57507</v>
+        <v>95683</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2429,46 +2442,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Otterstad 1:7, Vg</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>393947</v>
+        <v>394154</v>
       </c>
       <c r="R17" t="n">
-        <v>6504308</v>
+        <v>6504379</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2531,7 +2536,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123317810</v>
+        <v>123317815</v>
       </c>
       <c r="B18" t="n">
         <v>98079</v>
@@ -2566,7 +2571,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2583,10 +2588,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>394012</v>
+        <v>394144</v>
       </c>
       <c r="R18" t="n">
-        <v>6504408</v>
+        <v>6504350</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2650,7 +2655,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123317809</v>
+        <v>123317821</v>
       </c>
       <c r="B19" t="n">
         <v>98079</v>
@@ -2685,7 +2690,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2702,10 +2707,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>394112</v>
+        <v>394117</v>
       </c>
       <c r="R19" t="n">
-        <v>6504193</v>
+        <v>6504168</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2769,7 +2774,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123317812</v>
+        <v>123317818</v>
       </c>
       <c r="B20" t="n">
         <v>98079</v>
@@ -2804,7 +2809,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2821,10 +2826,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>394109</v>
+        <v>394150</v>
       </c>
       <c r="R20" t="n">
-        <v>6504115</v>
+        <v>6504272</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2888,7 +2893,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123317824</v>
+        <v>123317816</v>
       </c>
       <c r="B21" t="n">
         <v>98079</v>
@@ -2923,7 +2928,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2940,10 +2945,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>394136</v>
+        <v>394154</v>
       </c>
       <c r="R21" t="n">
-        <v>6504304</v>
+        <v>6504379</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -3007,10 +3012,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123317816</v>
+        <v>123317808</v>
       </c>
       <c r="B22" t="n">
-        <v>98079</v>
+        <v>57507</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3019,39 +3024,35 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3059,10 +3060,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>394154</v>
+        <v>393947</v>
       </c>
       <c r="R22" t="n">
-        <v>6504379</v>
+        <v>6504308</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3103,7 +3104,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3126,7 +3126,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123317825</v>
+        <v>123317822</v>
       </c>
       <c r="B23" t="n">
         <v>98079</v>
@@ -3161,7 +3161,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3178,10 +3178,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>394022</v>
+        <v>393947</v>
       </c>
       <c r="R23" t="n">
-        <v>6504439</v>
+        <v>6504225</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3459,10 +3459,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123856283</v>
+        <v>123856271</v>
       </c>
       <c r="B26" t="n">
-        <v>95683</v>
+        <v>91260</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3471,38 +3471,49 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2180</v>
+        <v>73</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Flavidoporia pulvinascens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Pilát) Audet</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Otterstad 1:7, Vg</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>394108</v>
+        <v>393935</v>
       </c>
       <c r="R26" t="n">
-        <v>6504382</v>
+        <v>6504313</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3543,6 +3554,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3566,10 +3578,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123856271</v>
+        <v>123856283</v>
       </c>
       <c r="B27" t="n">
-        <v>91260</v>
+        <v>95683</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3578,49 +3590,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>73</v>
+        <v>2180</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Veckticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Flavidoporia pulvinascens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Pilát) Audet</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Otterstad 1:7, Vg</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>393935</v>
+        <v>394108</v>
       </c>
       <c r="R27" t="n">
-        <v>6504313</v>
+        <v>6504382</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3661,7 +3662,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3678,7 +3678,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson, Jon Liljebäck, Ove Grönlund, Ada  Arenander, Liselotte Larsson</t>
+          <t>Liselotte Larsson , Ada  Arenander, Ove Grönlund, Jon Liljebäck, Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>

--- a/artfynd/A 8773-2025 artfynd.xlsx
+++ b/artfynd/A 8773-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123317804</v>
+        <v>123317808</v>
       </c>
       <c r="B2" t="n">
-        <v>91678</v>
+        <v>57507</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,46 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3298</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Otterstad 1:7, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>394108</v>
+        <v>393947</v>
       </c>
       <c r="R2" t="n">
-        <v>6504203</v>
+        <v>6504308</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -781,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123317811</v>
+        <v>123317828</v>
       </c>
       <c r="B3" t="n">
-        <v>98079</v>
+        <v>95683</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,50 +801,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Otterstad 1:7, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>394139</v>
+        <v>394154</v>
       </c>
       <c r="R3" t="n">
-        <v>6504335</v>
+        <v>6504379</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -877,7 +873,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -900,7 +895,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123317810</v>
+        <v>123317818</v>
       </c>
       <c r="B4" t="n">
         <v>98079</v>
@@ -935,7 +930,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -952,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>394012</v>
+        <v>394150</v>
       </c>
       <c r="R4" t="n">
-        <v>6504408</v>
+        <v>6504272</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -1019,7 +1014,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123317809</v>
+        <v>123317813</v>
       </c>
       <c r="B5" t="n">
         <v>98079</v>
@@ -1054,7 +1049,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1071,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>394112</v>
+        <v>394088</v>
       </c>
       <c r="R5" t="n">
-        <v>6504193</v>
+        <v>6504114</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1138,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123317801</v>
+        <v>123317814</v>
       </c>
       <c r="B6" t="n">
-        <v>95323</v>
+        <v>98079</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1150,38 +1145,50 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2810</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Otterstad 1:7, Vg</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>393999</v>
+        <v>394108</v>
       </c>
       <c r="R6" t="n">
-        <v>6504375</v>
+        <v>6504203</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1222,6 +1229,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1233,17 +1241,21 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Jon Liljebäck, Ada  Arenander, Kurt-Anders Johansson, Liselotte Larsson , Ove Grönlund, Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Skogsgruppen Skaraborg</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123317814</v>
+        <v>123317801</v>
       </c>
       <c r="B7" t="n">
-        <v>98079</v>
+        <v>95323</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1252,50 +1264,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>2810</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Otterstad 1:7, Vg</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>394108</v>
+        <v>393999</v>
       </c>
       <c r="R7" t="n">
-        <v>6504203</v>
+        <v>6504375</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1336,7 +1336,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1348,18 +1347,14 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jon Liljebäck, Ada  Arenander, Kurt-Anders Johansson, Liselotte Larsson , Ove Grönlund, Rolf-Göran Carlsson</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Skogsgruppen Skaraborg</t>
-        </is>
-      </c>
+          <t>Jon Liljebäck</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123317823</v>
+        <v>123317810</v>
       </c>
       <c r="B8" t="n">
         <v>98079</v>
@@ -1394,7 +1389,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>33</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1411,10 +1406,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>394108</v>
+        <v>394012</v>
       </c>
       <c r="R8" t="n">
-        <v>6504389</v>
+        <v>6504408</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1478,7 +1473,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123317825</v>
+        <v>123317815</v>
       </c>
       <c r="B9" t="n">
         <v>98079</v>
@@ -1513,7 +1508,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1530,10 +1525,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>394022</v>
+        <v>394144</v>
       </c>
       <c r="R9" t="n">
-        <v>6504439</v>
+        <v>6504350</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1597,7 +1592,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123317820</v>
+        <v>123317819</v>
       </c>
       <c r="B10" t="n">
         <v>98079</v>
@@ -1632,7 +1627,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1649,10 +1644,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>394159</v>
+        <v>394087</v>
       </c>
       <c r="R10" t="n">
-        <v>6504371</v>
+        <v>6504109</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1716,10 +1711,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123317819</v>
+        <v>123317827</v>
       </c>
       <c r="B11" t="n">
-        <v>98079</v>
+        <v>105095</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1728,30 +1723,30 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1768,10 +1763,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>394087</v>
+        <v>394111</v>
       </c>
       <c r="R11" t="n">
-        <v>6504109</v>
+        <v>6504177</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1954,7 +1949,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123317813</v>
+        <v>123317822</v>
       </c>
       <c r="B13" t="n">
         <v>98079</v>
@@ -1989,7 +1984,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2006,10 +2001,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>394088</v>
+        <v>393947</v>
       </c>
       <c r="R13" t="n">
-        <v>6504114</v>
+        <v>6504225</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2073,10 +2068,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123317827</v>
+        <v>123317809</v>
       </c>
       <c r="B14" t="n">
-        <v>105095</v>
+        <v>98079</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2085,30 +2080,30 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>42</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2125,10 +2120,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>394111</v>
+        <v>394112</v>
       </c>
       <c r="R14" t="n">
-        <v>6504177</v>
+        <v>6504193</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2192,10 +2187,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123317817</v>
+        <v>123317804</v>
       </c>
       <c r="B15" t="n">
-        <v>98079</v>
+        <v>91678</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2204,50 +2199,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Otterstad 1:7, Vg</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>394139</v>
+        <v>394108</v>
       </c>
       <c r="R15" t="n">
-        <v>6504327</v>
+        <v>6504203</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2288,7 +2271,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2311,7 +2293,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123317824</v>
+        <v>123317821</v>
       </c>
       <c r="B16" t="n">
         <v>98079</v>
@@ -2346,7 +2328,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2363,10 +2345,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>394136</v>
+        <v>394117</v>
       </c>
       <c r="R16" t="n">
-        <v>6504304</v>
+        <v>6504168</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2430,10 +2412,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123317828</v>
+        <v>123317817</v>
       </c>
       <c r="B17" t="n">
-        <v>95683</v>
+        <v>98079</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2442,38 +2424,50 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Otterstad 1:7, Vg</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>394154</v>
+        <v>394139</v>
       </c>
       <c r="R17" t="n">
-        <v>6504379</v>
+        <v>6504327</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2514,6 +2508,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2536,7 +2531,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123317815</v>
+        <v>123317811</v>
       </c>
       <c r="B18" t="n">
         <v>98079</v>
@@ -2571,7 +2566,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>28</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2588,10 +2583,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>394144</v>
+        <v>394139</v>
       </c>
       <c r="R18" t="n">
-        <v>6504350</v>
+        <v>6504335</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2655,7 +2650,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123317821</v>
+        <v>123317816</v>
       </c>
       <c r="B19" t="n">
         <v>98079</v>
@@ -2690,7 +2685,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2707,10 +2702,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>394117</v>
+        <v>394154</v>
       </c>
       <c r="R19" t="n">
-        <v>6504168</v>
+        <v>6504379</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2774,7 +2769,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123317818</v>
+        <v>123317823</v>
       </c>
       <c r="B20" t="n">
         <v>98079</v>
@@ -2809,7 +2804,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2826,10 +2821,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>394150</v>
+        <v>394108</v>
       </c>
       <c r="R20" t="n">
-        <v>6504272</v>
+        <v>6504389</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2893,7 +2888,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123317816</v>
+        <v>123317824</v>
       </c>
       <c r="B21" t="n">
         <v>98079</v>
@@ -2928,7 +2923,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2945,10 +2940,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>394154</v>
+        <v>394136</v>
       </c>
       <c r="R21" t="n">
-        <v>6504379</v>
+        <v>6504304</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -3012,10 +3007,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123317808</v>
+        <v>123317820</v>
       </c>
       <c r="B22" t="n">
-        <v>57507</v>
+        <v>98079</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3024,35 +3019,39 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3060,10 +3059,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>393947</v>
+        <v>394159</v>
       </c>
       <c r="R22" t="n">
-        <v>6504308</v>
+        <v>6504371</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3104,6 +3103,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3126,7 +3126,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123317822</v>
+        <v>123317825</v>
       </c>
       <c r="B23" t="n">
         <v>98079</v>
@@ -3161,7 +3161,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3178,10 +3178,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>393947</v>
+        <v>394022</v>
       </c>
       <c r="R23" t="n">
-        <v>6504225</v>
+        <v>6504439</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3345,17 +3345,17 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson, Jon Liljebäck, Ove Grönlund, Ada  Arenander, Liselotte Larsson</t>
+          <t>Liselotte Larsson , Kurt-Anders Johansson, Rolf-Göran Carlsson, Jon Liljebäck, Ove Grönlund, Ada  Arenander</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123856275</v>
+        <v>123856271</v>
       </c>
       <c r="B25" t="n">
-        <v>95323</v>
+        <v>91260</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3364,38 +3364,49 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2810</v>
+        <v>73</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Flavidoporia pulvinascens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Pilát) Audet</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Otterstad 1:7, Vg</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>393991</v>
+        <v>393935</v>
       </c>
       <c r="R25" t="n">
-        <v>6504398</v>
+        <v>6504313</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3436,6 +3447,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3459,10 +3471,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123856271</v>
+        <v>123856283</v>
       </c>
       <c r="B26" t="n">
-        <v>91260</v>
+        <v>95683</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3471,49 +3483,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>73</v>
+        <v>2180</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Veckticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Flavidoporia pulvinascens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Pilát) Audet</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Otterstad 1:7, Vg</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>393935</v>
+        <v>394108</v>
       </c>
       <c r="R26" t="n">
-        <v>6504313</v>
+        <v>6504382</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3554,7 +3555,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3578,10 +3578,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123856283</v>
+        <v>123856275</v>
       </c>
       <c r="B27" t="n">
-        <v>95683</v>
+        <v>95323</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3594,21 +3594,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2180</v>
+        <v>2810</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3618,10 +3618,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>394108</v>
+        <v>393991</v>
       </c>
       <c r="R27" t="n">
-        <v>6504382</v>
+        <v>6504398</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3678,7 +3678,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Liselotte Larsson , Ada  Arenander, Ove Grönlund, Jon Liljebäck, Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson, Jon Liljebäck, Ove Grönlund, Ada  Arenander, Liselotte Larsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>

--- a/artfynd/A 8773-2025 artfynd.xlsx
+++ b/artfynd/A 8773-2025 artfynd.xlsx
@@ -3364,10 +3364,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123856275</v>
+        <v>123856283</v>
       </c>
       <c r="B25" t="n">
-        <v>95345</v>
+        <v>95705</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3380,21 +3380,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2810</v>
+        <v>2180</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3404,10 +3404,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>393991</v>
+        <v>394108</v>
       </c>
       <c r="R25" t="n">
-        <v>6504398</v>
+        <v>6504382</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3471,10 +3471,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123856283</v>
+        <v>123856275</v>
       </c>
       <c r="B26" t="n">
-        <v>95705</v>
+        <v>95345</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3487,21 +3487,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2180</v>
+        <v>2810</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3511,10 +3511,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>394108</v>
+        <v>393991</v>
       </c>
       <c r="R26" t="n">
-        <v>6504382</v>
+        <v>6504398</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>

--- a/artfynd/A 8773-2025 artfynd.xlsx
+++ b/artfynd/A 8773-2025 artfynd.xlsx
@@ -3245,10 +3245,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123856271</v>
+        <v>123856283</v>
       </c>
       <c r="B24" t="n">
-        <v>91282</v>
+        <v>95705</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3257,49 +3257,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>73</v>
+        <v>2180</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Veckticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Flavidoporia pulvinascens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Pilát) Audet</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Otterstad 1:7, Vg</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>393935</v>
+        <v>394108</v>
       </c>
       <c r="R24" t="n">
-        <v>6504313</v>
+        <v>6504382</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3340,7 +3329,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3357,17 +3345,17 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson, Jon Liljebäck, Ove Grönlund, Ada  Arenander, Liselotte Larsson</t>
+          <t>Liselotte Larsson , Ada  Arenander, Ove Grönlund, Jon Liljebäck, Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123856283</v>
+        <v>123856275</v>
       </c>
       <c r="B25" t="n">
-        <v>95705</v>
+        <v>95345</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3380,21 +3368,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2180</v>
+        <v>2810</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3404,10 +3392,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>394108</v>
+        <v>393991</v>
       </c>
       <c r="R25" t="n">
-        <v>6504382</v>
+        <v>6504398</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3471,10 +3459,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123856275</v>
+        <v>123856267</v>
       </c>
       <c r="B26" t="n">
-        <v>95345</v>
+        <v>91413</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3487,21 +3475,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2810</v>
+        <v>4217</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3511,10 +3499,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>393991</v>
+        <v>393959</v>
       </c>
       <c r="R26" t="n">
-        <v>6504398</v>
+        <v>6504224</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3578,10 +3566,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123856267</v>
+        <v>123856271</v>
       </c>
       <c r="B27" t="n">
-        <v>91413</v>
+        <v>91282</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3590,38 +3578,49 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4217</v>
+        <v>73</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Flavidoporia pulvinascens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Pilát) Audet</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Otterstad 1:7, Vg</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>393959</v>
+        <v>393935</v>
       </c>
       <c r="R27" t="n">
-        <v>6504224</v>
+        <v>6504313</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3662,6 +3661,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 8773-2025 artfynd.xlsx
+++ b/artfynd/A 8773-2025 artfynd.xlsx
@@ -3352,10 +3352,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123856275</v>
+        <v>123856267</v>
       </c>
       <c r="B25" t="n">
-        <v>95345</v>
+        <v>91413</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3368,21 +3368,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2810</v>
+        <v>4217</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3392,10 +3392,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>393991</v>
+        <v>393959</v>
       </c>
       <c r="R25" t="n">
-        <v>6504398</v>
+        <v>6504224</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3459,10 +3459,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123856267</v>
+        <v>123856275</v>
       </c>
       <c r="B26" t="n">
-        <v>91413</v>
+        <v>95345</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3475,21 +3475,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4217</v>
+        <v>2810</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3499,10 +3499,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>393959</v>
+        <v>393991</v>
       </c>
       <c r="R26" t="n">
-        <v>6504224</v>
+        <v>6504398</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
